--- a/05_App/benchmark/rera_benchmark.xlsx
+++ b/05_App/benchmark/rera_benchmark.xlsx
@@ -743,7 +743,11 @@
           <t>RERA Act 2016, Section 5 and Section 6</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -770,7 +774,11 @@
           <t>RERA Act 2016, Section 4(2)(l)(D)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -797,7 +805,11 @@
           <t>RERA Act 2016, Section 59(1)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -824,7 +836,11 @@
           <t>RERA Act 2016, Section 3(2)(a) and (b)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -851,7 +867,11 @@
           <t>RERA Act 2016, Section 18(1); State RERA Rules</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -878,7 +898,11 @@
           <t>RERA Act 2016, Section 9(6)</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -905,7 +929,11 @@
           <t>RERA Act 2016, Section 43</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -932,7 +960,11 @@
           <t>RERA Act 2016, Section 14(2)</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -959,7 +991,11 @@
           <t>RERA Act 2016, Section 29</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -986,7 +1022,11 @@
           <t>RERA Act 2016, Section 17</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -1013,7 +1053,11 @@
           <t>RERA Act 2016, Section 17(1)</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
@@ -1040,7 +1084,11 @@
           <t>RERA Act 2016, Section 2(k)</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="60" customHeight="1">
@@ -1067,7 +1115,11 @@
           <t>RERA Act 2016, Section 11(1) read with Rules</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="60" customHeight="1">
@@ -1094,7 +1146,11 @@
           <t>RERA Act 2016, Section 62</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
@@ -1121,7 +1177,11 @@
           <t>RERA Act 2016, Section 31; Limitation Act 1963</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="60" customHeight="1">
@@ -1148,7 +1208,11 @@
           <t>RERA Act 2016, Section 11(4)(e); State RERA Rules</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="60" customHeight="1">
@@ -1175,7 +1239,11 @@
           <t>RERA Act 2016, Section 14(3)</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -1202,7 +1270,11 @@
           <t>RERA Act 2016, Section 72</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
@@ -1229,7 +1301,11 @@
           <t>RERA Act 2016, Section 3; Proviso to Section 3(1)</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
           <t>A very common trap: many assume ongoing projects are exempt. They are not.</t>
@@ -1260,7 +1336,11 @@
           <t>RERA Act 2016, Section 4(2)(l)(D)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="inlineStr"/>
     </row>
     <row r="23" ht="60" customHeight="1">
@@ -1287,7 +1367,11 @@
           <t>RERA Act 2016, Sections 2(zk), 2(zm), 9, 10</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G23" s="5" t="inlineStr"/>
     </row>
     <row r="24" ht="60" customHeight="1">
@@ -1314,7 +1398,11 @@
           <t>RERA Act 2016, Sections 2(k), 12, 14</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G24" s="5" t="inlineStr"/>
     </row>
     <row r="25" ht="60" customHeight="1">
@@ -1341,7 +1429,11 @@
           <t>RERA Act 2016, Section 6</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G25" s="5" t="inlineStr"/>
     </row>
     <row r="26" ht="60" customHeight="1">
@@ -1368,7 +1460,11 @@
           <t>RERA Act 2016, Sections 11(5) and 18</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G26" s="5" t="inlineStr"/>
     </row>
     <row r="27" ht="60" customHeight="1">
@@ -1395,7 +1491,11 @@
           <t>RERA Act 2016, Sections 3 and 59</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G27" s="5" t="inlineStr"/>
     </row>
     <row r="28" ht="60" customHeight="1">
@@ -1422,7 +1522,11 @@
           <t>RERA Act 2016, Sections 43-58</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G28" s="5" t="inlineStr"/>
     </row>
     <row r="29" ht="60" customHeight="1">
@@ -1449,7 +1553,11 @@
           <t>RERA Act 2016, Section 15</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G29" s="5" t="inlineStr"/>
     </row>
     <row r="30" ht="60" customHeight="1">
@@ -1476,7 +1584,11 @@
           <t>RERA Act 2016, Section 2(k); Model Agreement for Sale (MOFA/state variants)</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G30" s="5" t="inlineStr"/>
     </row>
     <row r="31" ht="60" customHeight="1">
@@ -1503,7 +1615,11 @@
           <t>RERA Act 2016, Sections 29-40 (Authority), 71-72 (Adjudicating Officer)</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G31" s="5" t="inlineStr"/>
     </row>
     <row r="32" ht="60" customHeight="1">
@@ -1530,7 +1646,11 @@
           <t>RERA Act 2016, Sections 4 and 11</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G32" s="5" t="inlineStr"/>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -1557,7 +1677,11 @@
           <t>RERA Act 2016, Section 2 definitions; applicability provisions</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Many assume RERA applies only to residential projects.</t>
@@ -1588,7 +1712,11 @@
           <t>RERA Act 2016, Sections 2(n) and 17</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G34" s="5" t="inlineStr"/>
     </row>
     <row r="35" ht="60" customHeight="1">
@@ -1615,7 +1743,11 @@
           <t>RERA Act 2016, Section 16</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G35" s="5" t="inlineStr"/>
     </row>
     <row r="36" ht="60" customHeight="1">
@@ -1642,7 +1774,11 @@
           <t>RERA Act 2016, Section 10 and 62</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="60" customHeight="1">
@@ -1669,7 +1805,11 @@
           <t>RERA Act 2016, Section 2(d) and multiple governance sections</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G37" s="5" t="inlineStr"/>
     </row>
     <row r="38" ht="60" customHeight="1">
@@ -1696,7 +1836,11 @@
           <t>RERA Act 2016, Section 19; State apartment ownership laws</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G38" s="5" t="inlineStr"/>
     </row>
     <row r="39" ht="60" customHeight="1">
@@ -1723,7 +1867,11 @@
           <t>RERA Act 2016, Sections 2(zn) and 3</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G39" s="5" t="inlineStr"/>
     </row>
     <row r="40" ht="60" customHeight="1">
@@ -1750,7 +1898,11 @@
           <t>RERA Act 2016, Sections 4 and 5; State-specific authority orders</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G40" s="5" t="inlineStr"/>
     </row>
     <row r="41" ht="60" customHeight="1">
@@ -1777,7 +1929,11 @@
           <t>RERA Act 2016, Section 12 and 71</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G41" s="5" t="inlineStr"/>
     </row>
     <row r="42" ht="60" customHeight="1">
@@ -1804,7 +1960,11 @@
           <t>RERA Act 2016, Section 3; Karnataka RERA Authority orders</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr"/>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
           <t>Promoters use 'EOI' or 'token' labels to disguise pre-registration collection; this is still a violation.</t>
@@ -1835,7 +1995,11 @@
           <t>RERA Act 2016, Sections 6 and 18; State RERA Covid extensions</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
           <t>Covid is not a blanket excuse for delay beyond the specific extension period granted.</t>
@@ -1866,7 +2030,11 @@
           <t>RERA Act 2016, Section 10; Consumer Protection Act 2019</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G44" s="6" t="inlineStr"/>
     </row>
     <row r="45" ht="60" customHeight="1">
@@ -1893,7 +2061,11 @@
           <t>RERA Act 2016, Section 15</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G45" s="6" t="inlineStr"/>
     </row>
     <row r="46" ht="60" customHeight="1">
@@ -1920,7 +2092,11 @@
           <t>RERA Act 2016, Sections 12, 14, 18, 31</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G46" s="6" t="inlineStr"/>
     </row>
     <row r="47" ht="60" customHeight="1">
@@ -1947,7 +2123,11 @@
           <t>RERA Act 2016, Section 4(2)(l)(D)</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G47" s="6" t="inlineStr"/>
     </row>
     <row r="48" ht="60" customHeight="1">
@@ -1974,7 +2154,11 @@
           <t>RERA Act 2016, Section 18(1) and proviso</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr"/>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
           <t>Some promoters argue that if the buyer stays, they forfeit the interest claim. This is false.</t>
@@ -2005,7 +2189,11 @@
           <t>RERA Act 2016; IBC 2016, Section 14; Pioneer Urban Land v. Union of India (2019) SCC</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
           <t>RERA and IBC conflict is a common trap; IBC moratorium supersedes pending RERA proceedings.</t>
@@ -2036,7 +2224,11 @@
           <t>RERA Act 2016, Section 14(2)</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G50" s="6" t="inlineStr"/>
     </row>
     <row r="51" ht="60" customHeight="1">
@@ -2063,7 +2255,11 @@
           <t>RERA Act 2016, Section 3(2) read with the explanation/State rules</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
           <t>Phase-splitting to escape registration threshold is a well-known promoter tactic explicitly addressed by RERA.</t>
@@ -2094,7 +2290,11 @@
           <t>RERA Act 2016, Sections 17, 40, 63, 71</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G52" s="6" t="inlineStr"/>
     </row>
     <row r="53" ht="60" customHeight="1">
@@ -2121,7 +2321,11 @@
           <t>RERA Act 2016, Sections 12, 14, and 71</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G53" s="6" t="inlineStr"/>
     </row>
     <row r="54" ht="60" customHeight="1">
@@ -2148,7 +2352,11 @@
           <t>RERA Act 2016, Section 2(d) and 18</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G54" s="6" t="inlineStr"/>
     </row>
     <row r="55" ht="60" customHeight="1">
@@ -2175,7 +2383,11 @@
           <t>RERA Act 2016, Sections 7, 8, and 40</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G55" s="6" t="inlineStr"/>
     </row>
     <row r="56" ht="60" customHeight="1">
@@ -2202,7 +2414,11 @@
           <t>RERA Act 2016, Sections 11(4)(b), 12, 16, 71</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr"/>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G56" s="6" t="inlineStr"/>
     </row>
     <row r="57" ht="60" customHeight="1">
@@ -2229,7 +2445,11 @@
           <t>RERA Act 2016, Section 19; State RERA Model Agreement</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
           <t>Non-refundable clauses in their entirety are often not enforceable; RERA limits forfeiture.</t>
@@ -2260,7 +2480,11 @@
           <t>RERA Act 2016, Section 4; MahaRERA Rules and circulars on phased projects</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr"/>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G58" s="6" t="inlineStr"/>
     </row>
     <row r="59" ht="60" customHeight="1">
@@ -2287,7 +2511,11 @@
           <t>RERA Act 2016, Sections 5, 6, 59</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr"/>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G59" s="6" t="inlineStr"/>
     </row>
     <row r="60" ht="60" customHeight="1">
@@ -2314,7 +2542,11 @@
           <t>RERA Act 2016, Section 2(d) and 31; FEMA 1999</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr"/>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G60" s="6" t="inlineStr"/>
     </row>
     <row r="61" ht="60" customHeight="1">
@@ -2341,7 +2573,11 @@
           <t>RERA Act 2016, Section 3 proviso for ongoing projects</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G61" s="6" t="inlineStr"/>
     </row>
     <row r="62" ht="60" customHeight="1">
@@ -2368,7 +2604,11 @@
           <t>RERA Act 2016, Sections 3-17 progressively</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr"/>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G62" s="7" t="inlineStr"/>
     </row>
     <row r="63" ht="60" customHeight="1">
@@ -2395,7 +2635,11 @@
           <t>RERA Act 2016, Sections 7, 8, 15; IBC 2016, Sections 5(8), 7</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G63" s="7" t="inlineStr"/>
     </row>
     <row r="64" ht="60" customHeight="1">
@@ -2422,7 +2666,11 @@
           <t>RERA Act 2016, Section 18; State RERA Rules on interest rate</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
           <t>Accepting possession does not forfeit accrued interest claims for delay period.</t>
@@ -2453,7 +2701,11 @@
           <t>RERA Act 2016, Sections 2(zn), 3, 4(2)(l)(D)</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr"/>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G65" s="7" t="inlineStr"/>
     </row>
     <row r="66" ht="60" customHeight="1">
@@ -2480,7 +2732,11 @@
           <t>RERA Act 2016, Sections 43(5) and 40</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr"/>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
           <t>Appeal to REAT does not automatically stay Authority orders; explicit stay application is needed.</t>
@@ -2511,7 +2767,11 @@
           <t>RERA Act 2016, Sections 12, 18, 31, 71; RBI circular on subvention schemes</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr"/>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G67" s="7" t="inlineStr"/>
     </row>
     <row r="68" ht="60" customHeight="1">
@@ -2538,7 +2798,11 @@
           <t>RERA Act 2016, Sections 31-40; Consumer Protection Act 2019; CPC</t>
         </is>
       </c>
-      <c r="F68" s="7" t="inlineStr"/>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
           <t>Many assume RERA and Consumer Forum cannot run concurrently; they can for different reliefs.</t>
@@ -2569,7 +2833,11 @@
           <t>RERA Act 2016, Sections 14(2) and 18</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr"/>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G69" s="7" t="inlineStr"/>
     </row>
     <row r="70" ht="60" customHeight="1">
@@ -2596,7 +2864,11 @@
           <t>RERA Act 2016, Section 12; Consumer Protection Act 2019; IPC Section 420</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr"/>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G70" s="7" t="inlineStr"/>
     </row>
     <row r="71" ht="60" customHeight="1">
@@ -2623,7 +2895,11 @@
           <t>RERA Act 2016 provisions cited; RERA Annual Reports; academic reviews</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr"/>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G71" s="7" t="inlineStr"/>
     </row>
     <row r="72" ht="60" customHeight="1">
@@ -2650,7 +2926,11 @@
           <t>RERA Act 2016, Sections 40, 63, 64</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr"/>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G72" s="7" t="inlineStr"/>
     </row>
     <row r="73" ht="60" customHeight="1">
@@ -2677,7 +2957,11 @@
           <t>RERA Act 2016; Transfer of Property Act 1882, Section 54; Registration Act 1908</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr"/>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G73" s="7" t="inlineStr"/>
     </row>
     <row r="74" ht="60" customHeight="1">
@@ -2704,7 +2988,11 @@
           <t>RERA Act 2016, Section 4; doctrine of ultra vires; statutory interpretation principles</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr"/>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
           <t>States can modify RERA rules but cannot contradict the parent Act's explicit mandatory provisions.</t>
@@ -2735,7 +3023,11 @@
           <t>RERA Act 2016, Sections 2(zk) and 4; Company Law; agency principles</t>
         </is>
       </c>
-      <c r="F75" s="7" t="inlineStr"/>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G75" s="7" t="inlineStr"/>
     </row>
     <row r="76" ht="60" customHeight="1">
@@ -2762,7 +3054,11 @@
           <t>RERA Act 2016, Section 2(zk); Company law on corporate veil; IBC provisions on related parties</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr"/>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G76" s="7" t="inlineStr"/>
     </row>
     <row r="77" ht="60" customHeight="1">
@@ -2789,7 +3085,11 @@
           <t>RERA Act 2016, Section 6; NGT Act 2010; Consumer Protection Act 2019</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr"/>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G77" s="7" t="inlineStr"/>
     </row>
     <row r="78" ht="60" customHeight="1">
@@ -2816,7 +3116,11 @@
           <t>RERA Act 2016, Section 18; CPC Section 59; Indian Contract Act 1872</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr"/>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G78" s="7" t="inlineStr"/>
     </row>
     <row r="79" ht="60" customHeight="1">
@@ -2843,7 +3147,11 @@
           <t>RERA Act 2016, Sections 12, 19; Consumer Protection Act 2019</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr"/>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G79" s="7" t="inlineStr"/>
     </row>
     <row r="80" ht="60" customHeight="1">
@@ -2870,7 +3178,11 @@
           <t>Constitution of India Articles 254, 245-246; RERA Act 2016; town planning laws</t>
         </is>
       </c>
-      <c r="F80" s="7" t="inlineStr"/>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G80" s="7" t="inlineStr"/>
     </row>
     <row r="81" ht="60" customHeight="1">
@@ -2897,7 +3209,11 @@
           <t>IBC 2016, Sections 7, 14, 31; Pioneer Urban Land v. Union of India (2019) 8 SCC 416</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr"/>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>https://www.indiacode.nic.in/bitstream/123456789/6532/1/IBC_2016.pdf</t>
+        </is>
+      </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
           <t>RERA Authority orders do not prevail over NCLT-approved IBC Resolution Plans.</t>
@@ -2928,7 +3244,11 @@
           <t>RERA Act 2016, Section 3 proviso; interpretation principles for regulatory statutes</t>
         </is>
       </c>
-      <c r="F82" s="8" t="inlineStr"/>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
           <t>This is a common promoter defence in pre-RERA project cases, consistently rejected by courts.</t>
@@ -2959,7 +3279,11 @@
           <t>RERA Act 2016, Sections 2(zm) and 9</t>
         </is>
       </c>
-      <c r="F83" s="8" t="inlineStr"/>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
           <t>'Introduction' is a common label used to avoid agent registration; it falls within the statutory definition.</t>
@@ -2990,7 +3314,11 @@
           <t>RERA Act 2016 (no limitation provision); Limitation Act 1963, Section 22 on continuing breach</t>
         </is>
       </c>
-      <c r="F84" s="8" t="inlineStr"/>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
           <t>Promoters frequently cite non-existent one-year limitation periods; RERA has no such provision and delay is a continuing cause of action.</t>
@@ -3021,7 +3349,11 @@
           <t>RERA Act 2016, Sections 18, 40, 59-65; principles of regulatory enforcement</t>
         </is>
       </c>
-      <c r="F85" s="8" t="inlineStr"/>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G85" s="8" t="inlineStr"/>
     </row>
     <row r="86" ht="60" customHeight="1">
@@ -3048,7 +3380,11 @@
           <t>RERA Act 2016, Section 31; Arbitration and Conciliation Act 1996; Vijay Karia v. Prysmian Cavi (Supreme Court) on arbitrability</t>
         </is>
       </c>
-      <c r="F86" s="8" t="inlineStr"/>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
           <t>Arbitration clauses in sale agreements are routinely used by promoters to try to block RERA complaints.</t>
@@ -3079,7 +3415,11 @@
           <t>RERA Act 2016, Sections 11(4) and 14; Consumer Protection Act 2019; Transfer of Property Act</t>
         </is>
       </c>
-      <c r="F87" s="8" t="inlineStr"/>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
           <t>RERA protects agreement-based and sanctioned-plan rights; undocumented 'gifts' have weaker protection.</t>
@@ -3110,7 +3450,11 @@
           <t>RERA Act 2016; Constitution of India, Articles 246, 254</t>
         </is>
       </c>
-      <c r="F88" s="8" t="inlineStr"/>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
           <t>RERA's constitutional validity cannot be overridden by State law without Presidential Assent.</t>
@@ -3141,7 +3485,11 @@
           <t>RERA Act 2016, Sections 18, 59, 71; distinction between public penalty and private remedy</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr"/>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
           <t>Paying RERA penalties ≠ discharging obligations to allottees; this is a fundamental confusion of public and private law.</t>
@@ -3172,7 +3520,11 @@
           <t>RERA Act 2016, Sections 14(3), 17, 18</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr"/>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
           <t>CC does not discharge all RERA obligations; warranty, conveyance, and past interest claims survive.</t>
@@ -3203,7 +3555,11 @@
           <t>RERA Act 2016, Section 31</t>
         </is>
       </c>
-      <c r="F91" s="8" t="inlineStr"/>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
           <t>A fundamental false claim about RERA's complaint jurisdiction.</t>
@@ -3234,7 +3590,11 @@
           <t>RERA Act 2016, Sections 20, 31; statutory jurisdiction cannot be contracted away</t>
         </is>
       </c>
-      <c r="F92" s="8" t="inlineStr"/>
+      <c r="F92" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G92" s="8" t="inlineStr"/>
     </row>
     <row r="93" ht="60" customHeight="1">
@@ -3261,7 +3621,11 @@
           <t>RERA Act 2016, Section 18; Indian Contract Act - waiver of statutory rights</t>
         </is>
       </c>
-      <c r="F93" s="8" t="inlineStr"/>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G93" s="8" t="inlineStr"/>
     </row>
     <row r="94" ht="60" customHeight="1">
@@ -3288,7 +3652,11 @@
           <t>RERA Act 2016, Section 3; multiple RERA Authority orders on threshold manipulation</t>
         </is>
       </c>
-      <c r="F94" s="8" t="inlineStr"/>
+      <c r="F94" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G94" s="8" t="inlineStr"/>
     </row>
     <row r="95" ht="60" customHeight="1">
@@ -3315,7 +3683,11 @@
           <t>RERA Act 2016, Sections 11, 35, 38, 60</t>
         </is>
       </c>
-      <c r="F95" s="8" t="inlineStr"/>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
           <t>RERA Authority's suo motu powers are often underappreciated; the Authority need not wait for complaints.</t>
@@ -3346,7 +3718,11 @@
           <t>RERA Act 2016, Sections 3 and 12; statutory interpretation - natural and ordinary meaning</t>
         </is>
       </c>
-      <c r="F96" s="8" t="inlineStr"/>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
           <t>Narrow textual arguments about undefined terms rarely succeed against clear legislative intent.</t>
@@ -3377,7 +3753,11 @@
           <t>RERA Act 2016, Sections 3, 59(1) and (2)</t>
         </is>
       </c>
-      <c r="F97" s="8" t="inlineStr"/>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
           <t>Treating penalties as acceptable costs to avoid compliance is a classic regulatory arbitrage argument that courts and authorities always reject.</t>
@@ -3408,7 +3788,11 @@
           <t>RERA Act 2016, Section 3(2)(c) and interpretation by multiple RERA Authorities</t>
         </is>
       </c>
-      <c r="F98" s="8" t="inlineStr"/>
+      <c r="F98" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
           <t>Phase 1 CC does not exempt Phase 2 from RERA registration.</t>
@@ -3439,7 +3823,11 @@
           <t>RERA Act 2016, Sections 2(zk) and 64</t>
         </is>
       </c>
-      <c r="F99" s="8" t="inlineStr"/>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G99" s="8" t="inlineStr"/>
     </row>
     <row r="100" ht="60" customHeight="1">
@@ -3466,7 +3854,11 @@
           <t>RERA Act 2016, Section 36; natural justice principles; judicial review</t>
         </is>
       </c>
-      <c r="F100" s="8" t="inlineStr"/>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G100" s="8" t="inlineStr"/>
     </row>
     <row r="101" ht="60" customHeight="1">
@@ -3493,7 +3885,11 @@
           <t>RERA Act 2016, Section 18; Indian Contract Act 1872, Section 23; statutory construction</t>
         </is>
       </c>
-      <c r="F101" s="8" t="inlineStr"/>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
           <t>Statutory rights cannot be waived by contract, however both parties signed it.</t>
@@ -3616,7 +4012,11 @@
           <t>RERA Act 2016, Section 5 and Section 6</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -3643,7 +4043,11 @@
           <t>RERA Act 2016, Section 4(2)(l)(D)</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -3670,7 +4074,11 @@
           <t>RERA Act 2016, Section 59(1)</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -3697,7 +4105,11 @@
           <t>RERA Act 2016, Section 3(2)(a) and (b)</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -3724,7 +4136,11 @@
           <t>RERA Act 2016, Section 18(1); State RERA Rules</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -3751,7 +4167,11 @@
           <t>RERA Act 2016, Section 9(6)</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -3778,7 +4198,11 @@
           <t>RERA Act 2016, Section 43</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -3805,7 +4229,11 @@
           <t>RERA Act 2016, Section 14(2)</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -3832,7 +4260,11 @@
           <t>RERA Act 2016, Section 29</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -3859,7 +4291,11 @@
           <t>RERA Act 2016, Section 17</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -3886,7 +4322,11 @@
           <t>RERA Act 2016, Section 17(1)</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
@@ -3913,7 +4353,11 @@
           <t>RERA Act 2016, Section 2(k)</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="60" customHeight="1">
@@ -3940,7 +4384,11 @@
           <t>RERA Act 2016, Section 11(1) read with Rules</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="60" customHeight="1">
@@ -3967,7 +4415,11 @@
           <t>RERA Act 2016, Section 62</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
@@ -3994,7 +4446,11 @@
           <t>RERA Act 2016, Section 31; Limitation Act 1963</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="60" customHeight="1">
@@ -4021,7 +4477,11 @@
           <t>RERA Act 2016, Section 11(4)(e); State RERA Rules</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19" ht="60" customHeight="1">
@@ -4048,7 +4508,11 @@
           <t>RERA Act 2016, Section 14(3)</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -4075,7 +4539,11 @@
           <t>RERA Act 2016, Section 72</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
@@ -4102,7 +4570,11 @@
           <t>RERA Act 2016, Section 3; Proviso to Section 3(1)</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
           <t>A very common trap: many assume ongoing projects are exempt. They are not.</t>
@@ -4194,7 +4666,11 @@
           <t>RERA Act 2016, Section 4(2)(l)(D)</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr"/>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G2" s="5" t="inlineStr"/>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -4221,7 +4697,11 @@
           <t>RERA Act 2016, Sections 2(zk), 2(zm), 9, 10</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -4248,7 +4728,11 @@
           <t>RERA Act 2016, Sections 2(k), 12, 14</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -4275,7 +4759,11 @@
           <t>RERA Act 2016, Section 6</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -4302,7 +4790,11 @@
           <t>RERA Act 2016, Sections 11(5) and 18</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -4329,7 +4821,11 @@
           <t>RERA Act 2016, Sections 3 and 59</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -4356,7 +4852,11 @@
           <t>RERA Act 2016, Sections 43-58</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -4383,7 +4883,11 @@
           <t>RERA Act 2016, Section 15</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -4410,7 +4914,11 @@
           <t>RERA Act 2016, Section 2(k); Model Agreement for Sale (MOFA/state variants)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -4437,7 +4945,11 @@
           <t>RERA Act 2016, Sections 29-40 (Authority), 71-72 (Adjudicating Officer)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -4464,7 +4976,11 @@
           <t>RERA Act 2016, Sections 4 and 11</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -4491,7 +5007,11 @@
           <t>RERA Act 2016, Section 2 definitions; applicability provisions</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Many assume RERA applies only to residential projects.</t>
@@ -4522,7 +5042,11 @@
           <t>RERA Act 2016, Sections 2(n) and 17</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="60" customHeight="1">
@@ -4549,7 +5073,11 @@
           <t>RERA Act 2016, Section 16</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G15" s="5" t="inlineStr"/>
     </row>
     <row r="16" ht="60" customHeight="1">
@@ -4576,7 +5104,11 @@
           <t>RERA Act 2016, Section 10 and 62</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
@@ -4603,7 +5135,11 @@
           <t>RERA Act 2016, Section 2(d) and multiple governance sections</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G17" s="5" t="inlineStr"/>
     </row>
     <row r="18" ht="60" customHeight="1">
@@ -4630,7 +5166,11 @@
           <t>RERA Act 2016, Section 19; State apartment ownership laws</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="60" customHeight="1">
@@ -4657,7 +5197,11 @@
           <t>RERA Act 2016, Sections 2(zn) and 3</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G19" s="5" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -4684,7 +5228,11 @@
           <t>RERA Act 2016, Sections 4 and 5; State-specific authority orders</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
@@ -4711,7 +5259,11 @@
           <t>RERA Act 2016, Section 12 and 71</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G21" s="5" t="inlineStr"/>
     </row>
   </sheetData>
@@ -4799,7 +5351,11 @@
           <t>RERA Act 2016, Section 3; Karnataka RERA Authority orders</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Promoters use 'EOI' or 'token' labels to disguise pre-registration collection; this is still a violation.</t>
@@ -4830,7 +5386,11 @@
           <t>RERA Act 2016, Sections 6 and 18; State RERA Covid extensions</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Covid is not a blanket excuse for delay beyond the specific extension period granted.</t>
@@ -4861,7 +5421,11 @@
           <t>RERA Act 2016, Section 10; Consumer Protection Act 2019</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -4888,7 +5452,11 @@
           <t>RERA Act 2016, Section 15</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G5" s="6" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -4915,7 +5483,11 @@
           <t>RERA Act 2016, Sections 12, 14, 18, 31</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
@@ -4942,7 +5514,11 @@
           <t>RERA Act 2016, Section 4(2)(l)(D)</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -4969,7 +5545,11 @@
           <t>RERA Act 2016, Section 18(1) and proviso</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>Some promoters argue that if the buyer stays, they forfeit the interest claim. This is false.</t>
@@ -5000,7 +5580,11 @@
           <t>RERA Act 2016; IBC 2016, Section 14; Pioneer Urban Land v. Union of India (2019) SCC</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>RERA and IBC conflict is a common trap; IBC moratorium supersedes pending RERA proceedings.</t>
@@ -5031,7 +5615,11 @@
           <t>RERA Act 2016, Section 14(2)</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -5058,7 +5646,11 @@
           <t>RERA Act 2016, Section 3(2) read with the explanation/State rules</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Phase-splitting to escape registration threshold is a well-known promoter tactic explicitly addressed by RERA.</t>
@@ -5089,7 +5681,11 @@
           <t>RERA Act 2016, Sections 17, 40, 63, 71</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -5116,7 +5712,11 @@
           <t>RERA Act 2016, Sections 12, 14, and 71</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
@@ -5143,7 +5743,11 @@
           <t>RERA Act 2016, Section 2(d) and 18</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr"/>
     </row>
     <row r="15" ht="60" customHeight="1">
@@ -5170,7 +5774,11 @@
           <t>RERA Act 2016, Sections 7, 8, and 40</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="60" customHeight="1">
@@ -5197,7 +5805,11 @@
           <t>RERA Act 2016, Sections 11(4)(b), 12, 16, 71</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
@@ -5224,7 +5836,11 @@
           <t>RERA Act 2016, Section 19; State RERA Model Agreement</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Non-refundable clauses in their entirety are often not enforceable; RERA limits forfeiture.</t>
@@ -5255,7 +5871,11 @@
           <t>RERA Act 2016, Section 4; MahaRERA Rules and circulars on phased projects</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="60" customHeight="1">
@@ -5282,7 +5902,11 @@
           <t>RERA Act 2016, Sections 5, 6, 59</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -5309,7 +5933,11 @@
           <t>RERA Act 2016, Section 2(d) and 31; FEMA 1999</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
@@ -5336,7 +5964,11 @@
           <t>RERA Act 2016, Section 3 proviso for ongoing projects</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5424,7 +6056,11 @@
           <t>RERA Act 2016, Sections 3-17 progressively</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr"/>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G2" s="7" t="inlineStr"/>
     </row>
     <row r="3" ht="60" customHeight="1">
@@ -5451,7 +6087,11 @@
           <t>RERA Act 2016, Sections 7, 8, 15; IBC 2016, Sections 5(8), 7</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G3" s="7" t="inlineStr"/>
     </row>
     <row r="4" ht="60" customHeight="1">
@@ -5478,7 +6118,11 @@
           <t>RERA Act 2016, Section 18; State RERA Rules on interest rate</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Accepting possession does not forfeit accrued interest claims for delay period.</t>
@@ -5509,7 +6153,11 @@
           <t>RERA Act 2016, Sections 2(zn), 3, 4(2)(l)(D)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -5536,7 +6184,11 @@
           <t>RERA Act 2016, Sections 43(5) and 40</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
           <t>Appeal to REAT does not automatically stay Authority orders; explicit stay application is needed.</t>
@@ -5567,7 +6219,11 @@
           <t>RERA Act 2016, Sections 12, 18, 31, 71; RBI circular on subvention schemes</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -5594,7 +6250,11 @@
           <t>RERA Act 2016, Sections 31-40; Consumer Protection Act 2019; CPC</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
           <t>Many assume RERA and Consumer Forum cannot run concurrently; they can for different reliefs.</t>
@@ -5625,7 +6285,11 @@
           <t>RERA Act 2016, Sections 14(2) and 18</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
@@ -5652,7 +6316,11 @@
           <t>RERA Act 2016, Section 12; Consumer Protection Act 2019; IPC Section 420</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G10" s="7" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
@@ -5679,7 +6347,11 @@
           <t>RERA Act 2016 provisions cited; RERA Annual Reports; academic reviews</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
@@ -5706,7 +6378,11 @@
           <t>RERA Act 2016, Sections 40, 63, 64</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G12" s="7" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -5733,7 +6409,11 @@
           <t>RERA Act 2016; Transfer of Property Act 1882, Section 54; Registration Act 1908</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
@@ -5760,7 +6440,11 @@
           <t>RERA Act 2016, Section 4; doctrine of ultra vires; statutory interpretation principles</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
           <t>States can modify RERA rules but cannot contradict the parent Act's explicit mandatory provisions.</t>
@@ -5791,7 +6475,11 @@
           <t>RERA Act 2016, Sections 2(zk) and 4; Company Law; agency principles</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="60" customHeight="1">
@@ -5818,7 +6506,11 @@
           <t>RERA Act 2016, Section 2(zk); Company law on corporate veil; IBC provisions on related parties</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G16" s="7" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
@@ -5845,7 +6537,11 @@
           <t>RERA Act 2016, Section 6; NGT Act 2010; Consumer Protection Act 2019</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr"/>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G17" s="7" t="inlineStr"/>
     </row>
     <row r="18" ht="60" customHeight="1">
@@ -5872,7 +6568,11 @@
           <t>RERA Act 2016, Section 18; CPC Section 59; Indian Contract Act 1872</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G18" s="7" t="inlineStr"/>
     </row>
     <row r="19" ht="60" customHeight="1">
@@ -5899,7 +6599,11 @@
           <t>RERA Act 2016, Sections 12, 19; Consumer Protection Act 2019</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr"/>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -5926,7 +6630,11 @@
           <t>Constitution of India Articles 254, 245-246; RERA Act 2016; town planning laws</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G20" s="7" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
@@ -5953,7 +6661,11 @@
           <t>IBC 2016, Sections 7, 14, 31; Pioneer Urban Land v. Union of India (2019) 8 SCC 416</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.indiacode.nic.in/bitstream/123456789/6532/1/IBC_2016.pdf</t>
+        </is>
+      </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
           <t>RERA Authority orders do not prevail over NCLT-approved IBC Resolution Plans.</t>
@@ -6045,7 +6757,11 @@
           <t>RERA Act 2016, Section 3 proviso; interpretation principles for regulatory statutes</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
           <t>This is a common promoter defence in pre-RERA project cases, consistently rejected by courts.</t>
@@ -6076,7 +6792,11 @@
           <t>RERA Act 2016, Sections 2(zm) and 9</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
           <t>'Introduction' is a common label used to avoid agent registration; it falls within the statutory definition.</t>
@@ -6107,7 +6827,11 @@
           <t>RERA Act 2016 (no limitation provision); Limitation Act 1963, Section 22 on continuing breach</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Promoters frequently cite non-existent one-year limitation periods; RERA has no such provision and delay is a continuing cause of action.</t>
@@ -6138,7 +6862,11 @@
           <t>RERA Act 2016, Sections 18, 40, 59-65; principles of regulatory enforcement</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G5" s="8" t="inlineStr"/>
     </row>
     <row r="6" ht="60" customHeight="1">
@@ -6165,7 +6893,11 @@
           <t>RERA Act 2016, Section 31; Arbitration and Conciliation Act 1996; Vijay Karia v. Prysmian Cavi (Supreme Court) on arbitrability</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Arbitration clauses in sale agreements are routinely used by promoters to try to block RERA complaints.</t>
@@ -6196,7 +6928,11 @@
           <t>RERA Act 2016, Sections 11(4) and 14; Consumer Protection Act 2019; Transfer of Property Act</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
           <t>RERA protects agreement-based and sanctioned-plan rights; undocumented 'gifts' have weaker protection.</t>
@@ -6227,7 +6963,11 @@
           <t>RERA Act 2016; Constitution of India, Articles 246, 254</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
           <t>RERA's constitutional validity cannot be overridden by State law without Presidential Assent.</t>
@@ -6258,7 +6998,11 @@
           <t>RERA Act 2016, Sections 18, 59, 71; distinction between public penalty and private remedy</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Paying RERA penalties ≠ discharging obligations to allottees; this is a fundamental confusion of public and private law.</t>
@@ -6289,7 +7033,11 @@
           <t>RERA Act 2016, Sections 14(3), 17, 18</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
           <t>CC does not discharge all RERA obligations; warranty, conveyance, and past interest claims survive.</t>
@@ -6320,7 +7068,11 @@
           <t>RERA Act 2016, Section 31</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
           <t>A fundamental false claim about RERA's complaint jurisdiction.</t>
@@ -6351,7 +7103,11 @@
           <t>RERA Act 2016, Sections 20, 31; statutory jurisdiction cannot be contracted away</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -6378,7 +7134,11 @@
           <t>RERA Act 2016, Section 18; Indian Contract Act - waiver of statutory rights</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G13" s="8" t="inlineStr"/>
     </row>
     <row r="14" ht="60" customHeight="1">
@@ -6405,7 +7165,11 @@
           <t>RERA Act 2016, Section 3; multiple RERA Authority orders on threshold manipulation</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G14" s="8" t="inlineStr"/>
     </row>
     <row r="15" ht="60" customHeight="1">
@@ -6432,7 +7196,11 @@
           <t>RERA Act 2016, Sections 11, 35, 38, 60</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
           <t>RERA Authority's suo motu powers are often underappreciated; the Authority need not wait for complaints.</t>
@@ -6463,7 +7231,11 @@
           <t>RERA Act 2016, Sections 3 and 12; statutory interpretation - natural and ordinary meaning</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
           <t>Narrow textual arguments about undefined terms rarely succeed against clear legislative intent.</t>
@@ -6494,7 +7266,11 @@
           <t>RERA Act 2016, Sections 3, 59(1) and (2)</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
           <t>Treating penalties as acceptable costs to avoid compliance is a classic regulatory arbitrage argument that courts and authorities always reject.</t>
@@ -6525,7 +7301,11 @@
           <t>RERA Act 2016, Section 3(2)(c) and interpretation by multiple RERA Authorities</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
           <t>Phase 1 CC does not exempt Phase 2 from RERA registration.</t>
@@ -6556,7 +7336,11 @@
           <t>RERA Act 2016, Sections 2(zk) and 64</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G19" s="8" t="inlineStr"/>
     </row>
     <row r="20" ht="60" customHeight="1">
@@ -6583,7 +7367,11 @@
           <t>RERA Act 2016, Section 36; natural justice principles; judicial review</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G20" s="8" t="inlineStr"/>
     </row>
     <row r="21" ht="60" customHeight="1">
@@ -6610,7 +7398,11 @@
           <t>RERA Act 2016, Section 18; Indian Contract Act 1872, Section 23; statutory construction</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>https://rera.karnataka.gov.in/act</t>
+        </is>
+      </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
           <t>Statutory rights cannot be waived by contract, however both parties signed it.</t>
